--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_RMSEP.xlsx
@@ -1,211 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\X9.cis.beta.carotene\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV0_RMSEP</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -238,51 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -324,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -356,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -391,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -567,2436 +350,2539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>51.422177270737109</v>
+        <v>51.42217724937422</v>
       </c>
       <c r="C2">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D2">
-        <v>58.831475279204788</v>
+        <v>58.83147526366304</v>
       </c>
       <c r="E2">
-        <v>53.467037332485013</v>
+        <v>53.467037316233</v>
       </c>
       <c r="F2">
-        <v>51.640160897561437</v>
+        <v>51.64016087040633</v>
       </c>
       <c r="G2">
-        <v>50.102680843099989</v>
-      </c>
-      <c r="H2" s="2">
-        <v>48.955002919692433</v>
+        <v>50.10268082223563</v>
+      </c>
+      <c r="H2">
+        <v>48.95500289299114</v>
       </c>
       <c r="I2">
-        <v>47.559298443013468</v>
+        <v>47.55929844850239</v>
       </c>
       <c r="J2">
-        <v>46.416628963006708</v>
+        <v>46.41662901612657</v>
       </c>
       <c r="K2">
-        <v>46.380828448747913</v>
+        <v>46.38082849687823</v>
       </c>
       <c r="L2">
-        <v>45.262879885204008</v>
+        <v>45.26287993451778</v>
       </c>
       <c r="M2">
-        <v>45.592088365996318</v>
+        <v>45.59208838173711</v>
       </c>
       <c r="N2">
-        <v>46.309959723870001</v>
+        <v>46.30995972096332</v>
       </c>
       <c r="O2">
-        <v>48.183469068756281</v>
+        <v>48.18346903140804</v>
       </c>
       <c r="P2">
-        <v>51.904950964318942</v>
+        <v>51.90495099163857</v>
       </c>
       <c r="Q2">
-        <v>56.319818096863123</v>
+        <v>56.31981831191944</v>
       </c>
       <c r="R2">
-        <v>57.569835327008953</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
+        <v>57.56983563385898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>55.514135867055558</v>
+        <v>55.51413606953908</v>
       </c>
       <c r="C3">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D3" s="2">
-        <v>57.111395497132023</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D3">
+        <v>57.11139577403979</v>
       </c>
       <c r="E3">
-        <v>52.797495587926107</v>
+        <v>52.79749551944357</v>
       </c>
       <c r="F3">
-        <v>53.218185493851699</v>
+        <v>53.21818541895994</v>
       </c>
       <c r="G3">
-        <v>54.306796545477241</v>
+        <v>54.30679637200636</v>
       </c>
       <c r="H3">
-        <v>52.188785520910152</v>
+        <v>52.18878515305465</v>
       </c>
       <c r="I3">
-        <v>53.036638017981311</v>
+        <v>53.03663771733092</v>
       </c>
       <c r="J3">
-        <v>53.641261584905983</v>
+        <v>53.64126137672947</v>
       </c>
       <c r="K3">
-        <v>54.07891632058336</v>
+        <v>54.0789162707551</v>
       </c>
       <c r="L3">
-        <v>55.281333530686958</v>
+        <v>55.28133336400202</v>
       </c>
       <c r="M3">
-        <v>57.008268229504139</v>
+        <v>57.00826795051175</v>
       </c>
       <c r="N3">
-        <v>58.876164380634783</v>
+        <v>58.87616450531851</v>
       </c>
       <c r="O3">
-        <v>60.258701099436557</v>
+        <v>60.25870012243987</v>
       </c>
       <c r="P3">
-        <v>61.212841989165518</v>
+        <v>61.21284197760114</v>
       </c>
       <c r="Q3">
-        <v>61.717669120944393</v>
+        <v>61.7176690328159</v>
       </c>
       <c r="R3">
-        <v>61.263797031571563</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
+        <v>61.26379680041478</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>55.396015856818202</v>
+        <v>55.39601588300587</v>
       </c>
       <c r="C4">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D4">
-        <v>58.443969415885682</v>
+        <v>58.44396940611833</v>
       </c>
       <c r="E4">
-        <v>54.873511646479628</v>
+        <v>54.87351163920318</v>
       </c>
       <c r="F4">
-        <v>54.362211733612071</v>
+        <v>54.36221171323629</v>
       </c>
       <c r="G4">
-        <v>53.379898474642637</v>
-      </c>
-      <c r="H4" s="2">
-        <v>50.871180826535827</v>
+        <v>53.37989847342366</v>
+      </c>
+      <c r="H4">
+        <v>50.87118086236467</v>
       </c>
       <c r="I4">
-        <v>47.925912394389329</v>
+        <v>47.92591243923957</v>
       </c>
       <c r="J4">
-        <v>47.808510876463068</v>
+        <v>47.8085108179459</v>
       </c>
       <c r="K4">
-        <v>47.771781470121468</v>
+        <v>47.77178135082239</v>
       </c>
       <c r="L4">
-        <v>49.670265045700447</v>
+        <v>49.67026485722494</v>
       </c>
       <c r="M4">
-        <v>51.511688964500493</v>
+        <v>51.51168870780857</v>
       </c>
       <c r="N4">
-        <v>52.608267445431068</v>
+        <v>52.60826716944985</v>
       </c>
       <c r="O4">
-        <v>55.9103750292103</v>
+        <v>55.910374864221</v>
       </c>
       <c r="P4">
-        <v>58.814186015894592</v>
+        <v>58.8141859764899</v>
       </c>
       <c r="Q4">
-        <v>60.777304108027288</v>
+        <v>60.77730428141324</v>
       </c>
       <c r="R4">
-        <v>62.055464778071709</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
+        <v>62.05546522504434</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>53.865500939922157</v>
+        <v>53.86550092161866</v>
       </c>
       <c r="C5">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D5" s="2">
-        <v>53.08615928942303</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D5">
+        <v>53.08615926570465</v>
       </c>
       <c r="E5">
-        <v>53.92388983718525</v>
+        <v>53.92388978297265</v>
       </c>
       <c r="F5">
-        <v>53.786071324452152</v>
+        <v>53.7860712329798</v>
       </c>
       <c r="G5">
-        <v>53.110882770163613</v>
+        <v>53.11088275727796</v>
       </c>
       <c r="H5">
-        <v>51.022038392491559</v>
+        <v>51.02203822377487</v>
       </c>
       <c r="I5">
-        <v>50.355579404675836</v>
+        <v>50.35557931844559</v>
       </c>
       <c r="J5">
-        <v>50.394334777233396</v>
+        <v>50.39433466158717</v>
       </c>
       <c r="K5">
-        <v>50.930987730841693</v>
+        <v>50.93098777484246</v>
       </c>
       <c r="L5">
-        <v>53.045120003068327</v>
+        <v>53.04511973872379</v>
       </c>
       <c r="M5">
-        <v>55.060003805830313</v>
+        <v>55.06000415439025</v>
       </c>
       <c r="N5">
-        <v>56.389786815283152</v>
+        <v>56.38978773101857</v>
       </c>
       <c r="O5">
-        <v>56.642484119434599</v>
+        <v>56.64248554555829</v>
       </c>
       <c r="P5">
-        <v>56.146163671105917</v>
+        <v>56.1461653366202</v>
       </c>
       <c r="Q5">
-        <v>56.592627856097259</v>
+        <v>56.59263002457701</v>
       </c>
       <c r="R5">
-        <v>56.962423731146323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
+        <v>56.96242643317291</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>54.287954240743282</v>
+        <v>54.28795422687596</v>
       </c>
       <c r="C6">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D6" s="2">
-        <v>52.988902191974319</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D6">
+        <v>52.98890217911647</v>
       </c>
       <c r="E6">
-        <v>53.503339833496803</v>
+        <v>53.50333981100871</v>
       </c>
       <c r="F6">
-        <v>53.053567146978317</v>
+        <v>53.05356709361622</v>
       </c>
       <c r="G6">
-        <v>51.922786342027671</v>
+        <v>51.92278636562276</v>
       </c>
       <c r="H6">
-        <v>49.120347894217758</v>
+        <v>49.12034788606788</v>
       </c>
       <c r="I6">
-        <v>50.072145019199112</v>
+        <v>50.07214521416663</v>
       </c>
       <c r="J6">
-        <v>49.286563149650213</v>
+        <v>49.28656334754763</v>
       </c>
       <c r="K6">
-        <v>50.520877364397727</v>
+        <v>50.52087809765984</v>
       </c>
       <c r="L6">
-        <v>52.588768391146409</v>
+        <v>52.58876905379303</v>
       </c>
       <c r="M6">
-        <v>53.125728415176447</v>
+        <v>53.12572953880912</v>
       </c>
       <c r="N6">
-        <v>54.41937487496547</v>
+        <v>54.4193765164397</v>
       </c>
       <c r="O6">
-        <v>55.009614180477399</v>
+        <v>55.0096165452951</v>
       </c>
       <c r="P6">
-        <v>56.206276084801779</v>
+        <v>56.20628006739324</v>
       </c>
       <c r="Q6">
-        <v>56.695868840064527</v>
+        <v>56.69587385482821</v>
       </c>
       <c r="R6">
-        <v>57.784084089749868</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
+        <v>57.784090710004</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>50.919329330366288</v>
+        <v>50.91932930775337</v>
       </c>
       <c r="C7">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D7" s="3">
-        <v>58.36932817460999</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D7">
+        <v>58.3693281643864</v>
       </c>
       <c r="E7">
-        <v>53.766291031912353</v>
-      </c>
-      <c r="F7" s="2">
-        <v>49.933909627389752</v>
+        <v>53.76629101845695</v>
+      </c>
+      <c r="F7">
+        <v>49.93390960298782</v>
       </c>
       <c r="G7">
-        <v>48.521712997357447</v>
+        <v>48.52171296366665</v>
       </c>
       <c r="H7">
-        <v>46.929050564079482</v>
+        <v>46.92905055728919</v>
       </c>
       <c r="I7">
-        <v>45.889443497263002</v>
+        <v>45.88944352192245</v>
       </c>
       <c r="J7">
-        <v>45.758359917216751</v>
+        <v>45.75835993871861</v>
       </c>
       <c r="K7">
-        <v>45.140271305162607</v>
+        <v>45.14027129508895</v>
       </c>
       <c r="L7">
-        <v>45.342518127922943</v>
+        <v>45.3425181155048</v>
       </c>
       <c r="M7">
-        <v>47.098029169450818</v>
+        <v>47.09802894269549</v>
       </c>
       <c r="N7">
-        <v>48.502812973220252</v>
+        <v>48.50281260410055</v>
       </c>
       <c r="O7">
-        <v>49.354564103189333</v>
+        <v>49.35456385180313</v>
       </c>
       <c r="P7">
-        <v>52.947726109061009</v>
+        <v>52.94772620993928</v>
       </c>
       <c r="Q7">
-        <v>56.365490352355508</v>
+        <v>56.3654906076458</v>
       </c>
       <c r="R7">
-        <v>58.380384741686171</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
+        <v>58.38038537463449</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>52.626032691915441</v>
+        <v>52.6260326578406</v>
       </c>
       <c r="C8">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D8">
-        <v>56.402948605034098</v>
+        <v>56.40294861314517</v>
       </c>
       <c r="E8">
-        <v>54.444181247339692</v>
-      </c>
-      <c r="F8" s="2">
-        <v>50.274633837376051</v>
+        <v>54.4441812511719</v>
+      </c>
+      <c r="F8">
+        <v>50.27463379658373</v>
       </c>
       <c r="G8">
-        <v>48.45691764105748</v>
+        <v>48.45691761999191</v>
       </c>
       <c r="H8">
-        <v>48.103177707523493</v>
+        <v>48.10317770351666</v>
       </c>
       <c r="I8">
-        <v>47.503580616652322</v>
+        <v>47.50358064453796</v>
       </c>
       <c r="J8">
-        <v>47.119772456006316</v>
+        <v>47.11977241255763</v>
       </c>
       <c r="K8">
-        <v>48.000165154183989</v>
+        <v>48.00016520942001</v>
       </c>
       <c r="L8">
-        <v>50.292142632182042</v>
+        <v>50.29214280104225</v>
       </c>
       <c r="M8">
-        <v>53.390617487933461</v>
+        <v>53.39061745195739</v>
       </c>
       <c r="N8">
-        <v>54.996070163367989</v>
+        <v>54.9960703286629</v>
       </c>
       <c r="O8">
-        <v>56.458280495549232</v>
+        <v>56.45828087183508</v>
       </c>
       <c r="P8">
-        <v>59.423250235902621</v>
+        <v>59.42325057173232</v>
       </c>
       <c r="Q8">
-        <v>61.336077449782159</v>
+        <v>61.33607733672465</v>
       </c>
       <c r="R8">
-        <v>64.172558717922044</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
+        <v>64.17255814446031</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>52.147586676219532</v>
+        <v>52.14758664135541</v>
       </c>
       <c r="C9">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D9">
-        <v>56.399798500598322</v>
+        <v>56.39979850866578</v>
       </c>
       <c r="E9">
-        <v>54.324134334820258</v>
-      </c>
-      <c r="F9" s="2">
-        <v>50.121013070333248</v>
+        <v>54.32413433809364</v>
+      </c>
+      <c r="F9">
+        <v>50.12101302749831</v>
       </c>
       <c r="G9">
-        <v>48.342051351524333</v>
+        <v>48.3420513395041</v>
       </c>
       <c r="H9">
-        <v>48.057358309951951</v>
+        <v>48.0573583066918</v>
       </c>
       <c r="I9">
-        <v>47.346128223295231</v>
+        <v>47.34612829164936</v>
       </c>
       <c r="J9">
-        <v>46.648225325284272</v>
+        <v>46.64822533384026</v>
       </c>
       <c r="K9">
-        <v>47.016306464762607</v>
+        <v>47.01630654178562</v>
       </c>
       <c r="L9">
-        <v>47.625770966096887</v>
+        <v>47.62577108494427</v>
       </c>
       <c r="M9">
-        <v>49.336608153966637</v>
+        <v>49.33660822547974</v>
       </c>
       <c r="N9">
-        <v>50.947427033858752</v>
+        <v>50.94742751634122</v>
       </c>
       <c r="O9">
-        <v>52.522808322030613</v>
+        <v>52.5228095358342</v>
       </c>
       <c r="P9">
-        <v>54.620937679114292</v>
+        <v>54.62093968017423</v>
       </c>
       <c r="Q9">
-        <v>55.238122088114373</v>
+        <v>55.23812450096966</v>
       </c>
       <c r="R9">
-        <v>56.149268836217097</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
+        <v>56.14927136565451</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>52.143507239157991</v>
+        <v>52.14350720892187</v>
       </c>
       <c r="C10">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D10">
-        <v>56.284927735682068</v>
+        <v>56.28492774391209</v>
       </c>
       <c r="E10">
-        <v>54.281223655989201</v>
-      </c>
-      <c r="F10" s="2">
-        <v>50.296048853447992</v>
+        <v>54.28122365965979</v>
+      </c>
+      <c r="F10">
+        <v>50.29604881399565</v>
       </c>
       <c r="G10">
-        <v>48.545027969394731</v>
+        <v>48.54502796008615</v>
       </c>
       <c r="H10">
-        <v>48.254105731124902</v>
+        <v>48.25410573349939</v>
       </c>
       <c r="I10">
-        <v>47.499360428455248</v>
+        <v>47.49936051864051</v>
       </c>
       <c r="J10">
-        <v>46.628072852804721</v>
+        <v>46.6280728915894</v>
       </c>
       <c r="K10">
-        <v>47.093896348850812</v>
+        <v>47.09389643905448</v>
       </c>
       <c r="L10">
-        <v>47.66724685998966</v>
+        <v>47.66724683210187</v>
       </c>
       <c r="M10">
-        <v>49.28640870054199</v>
+        <v>49.28640888621851</v>
       </c>
       <c r="N10">
-        <v>50.816747864499163</v>
+        <v>50.81674834153038</v>
       </c>
       <c r="O10">
-        <v>52.357123191628602</v>
+        <v>52.35712438288576</v>
       </c>
       <c r="P10">
-        <v>54.115516218192582</v>
+        <v>54.11551806686522</v>
       </c>
       <c r="Q10">
-        <v>54.714444679196177</v>
+        <v>54.71444696334331</v>
       </c>
       <c r="R10">
-        <v>55.968828452375938</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>27</v>
+        <v>55.9688312598572</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>52.576103756007413</v>
+        <v>52.57610372814233</v>
       </c>
       <c r="C11">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D11">
-        <v>56.469953267232917</v>
+        <v>56.46995327560259</v>
       </c>
       <c r="E11">
-        <v>54.401376347804259</v>
-      </c>
-      <c r="F11" s="2">
-        <v>50.384188051490497</v>
+        <v>54.40137635188884</v>
+      </c>
+      <c r="F11">
+        <v>50.38418801521495</v>
       </c>
       <c r="G11">
-        <v>48.602658564824686</v>
+        <v>48.60265855907444</v>
       </c>
       <c r="H11">
-        <v>48.250889442279018</v>
+        <v>48.25088945726993</v>
       </c>
       <c r="I11">
-        <v>47.544356645609192</v>
+        <v>47.54435673935398</v>
       </c>
       <c r="J11">
-        <v>46.949988710060843</v>
+        <v>46.94998873735189</v>
       </c>
       <c r="K11">
-        <v>47.247370993718611</v>
+        <v>47.24737110971882</v>
       </c>
       <c r="L11">
-        <v>47.883615542350803</v>
+        <v>47.88361573797931</v>
       </c>
       <c r="M11">
-        <v>49.721228737362139</v>
+        <v>49.72122895787714</v>
       </c>
       <c r="N11">
-        <v>50.999380295697293</v>
+        <v>50.9993808610208</v>
       </c>
       <c r="O11">
-        <v>52.298758136985938</v>
+        <v>52.29875938967591</v>
       </c>
       <c r="P11">
-        <v>53.810776025419209</v>
+        <v>53.81077781632066</v>
       </c>
       <c r="Q11">
-        <v>53.943672007541451</v>
+        <v>53.94367392724384</v>
       </c>
       <c r="R11">
-        <v>55.360386473683882</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>28</v>
+        <v>55.36038849482443</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>53.424525766927196</v>
+        <v>53.42452571443091</v>
       </c>
       <c r="C12">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D12" s="2">
-        <v>52.172374158664063</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D12">
+        <v>52.17237412891339</v>
       </c>
       <c r="E12">
-        <v>52.770171731801007</v>
-      </c>
-      <c r="F12" s="3">
-        <v>51.285763534153773</v>
+        <v>52.77017164914034</v>
+      </c>
+      <c r="F12">
+        <v>51.28576349097275</v>
       </c>
       <c r="G12">
-        <v>50.308930649476387</v>
+        <v>50.30893059635741</v>
       </c>
       <c r="H12">
-        <v>47.870623564483267</v>
+        <v>47.8706233943624</v>
       </c>
       <c r="I12">
-        <v>47.50298205363508</v>
+        <v>47.502981960821</v>
       </c>
       <c r="J12">
-        <v>47.244486994698228</v>
+        <v>47.24448678720597</v>
       </c>
       <c r="K12">
-        <v>48.52678541097756</v>
+        <v>48.52678512814064</v>
       </c>
       <c r="L12">
-        <v>50.206167609152118</v>
+        <v>50.20616746109085</v>
       </c>
       <c r="M12">
-        <v>53.40864209876996</v>
+        <v>53.40864232536678</v>
       </c>
       <c r="N12">
-        <v>55.492839540520293</v>
+        <v>55.49283956820935</v>
       </c>
       <c r="O12">
-        <v>57.215860409863701</v>
+        <v>57.21586040335038</v>
       </c>
       <c r="P12">
-        <v>57.38277595200271</v>
+        <v>57.38277592411479</v>
       </c>
       <c r="Q12">
-        <v>58.591526266216697</v>
+        <v>58.59152644089281</v>
       </c>
       <c r="R12">
-        <v>60.753051260370277</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
+        <v>60.75305145469063</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>52.53396979433402</v>
+        <v>52.53396977170721</v>
       </c>
       <c r="C13">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D13" s="2">
-        <v>52.24384808821992</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D13">
+        <v>52.24384806983615</v>
       </c>
       <c r="E13">
-        <v>53.382897188955241</v>
-      </c>
-      <c r="F13" s="3">
-        <v>51.38849435245934</v>
+        <v>53.38289717089956</v>
+      </c>
+      <c r="F13">
+        <v>51.38849435352324</v>
       </c>
       <c r="G13">
-        <v>50.26200925389621</v>
+        <v>50.26200939888697</v>
       </c>
       <c r="H13">
-        <v>51.954475793868788</v>
+        <v>51.95447615211242</v>
       </c>
       <c r="I13">
-        <v>51.220119585888227</v>
+        <v>51.22011988484908</v>
       </c>
       <c r="J13">
-        <v>50.499039239170173</v>
+        <v>50.49903947515142</v>
       </c>
       <c r="K13">
-        <v>50.886260092789897</v>
+        <v>50.88626002657645</v>
       </c>
       <c r="L13">
-        <v>52.23466546366808</v>
+        <v>52.23466453573123</v>
       </c>
       <c r="M13">
-        <v>55.534331211603842</v>
+        <v>55.53432991680598</v>
       </c>
       <c r="N13">
-        <v>57.689249337620112</v>
+        <v>57.68924779640805</v>
       </c>
       <c r="O13">
-        <v>58.456185638707979</v>
+        <v>58.4561841077872</v>
       </c>
       <c r="P13">
-        <v>60.104316416687162</v>
+        <v>60.10431463660191</v>
       </c>
       <c r="Q13">
-        <v>61.579276957515873</v>
+        <v>61.57927436519448</v>
       </c>
       <c r="R13">
-        <v>63.602632890686387</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
+        <v>63.60262916243248</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>51.152724416464743</v>
+        <v>51.15272439787663</v>
       </c>
       <c r="C14">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D14">
-        <v>58.331256117909739</v>
+        <v>58.33125610796194</v>
       </c>
       <c r="E14">
-        <v>53.704378839993517</v>
-      </c>
-      <c r="F14" s="2">
-        <v>49.758499500306307</v>
-      </c>
-      <c r="G14" s="3">
-        <v>48.495676522322348</v>
+        <v>53.70437882683337</v>
+      </c>
+      <c r="F14">
+        <v>49.75849947359404</v>
+      </c>
+      <c r="G14">
+        <v>48.49567648935029</v>
       </c>
       <c r="H14">
-        <v>46.83439503332901</v>
+        <v>46.83439503765157</v>
       </c>
       <c r="I14">
-        <v>45.713381314564387</v>
+        <v>45.71338135425212</v>
       </c>
       <c r="J14">
-        <v>45.58428872594903</v>
+        <v>45.58428878412588</v>
       </c>
       <c r="K14">
-        <v>44.895703029391619</v>
+        <v>44.89570304720686</v>
       </c>
       <c r="L14">
-        <v>44.909354468755033</v>
+        <v>44.90935447025488</v>
       </c>
       <c r="M14">
-        <v>45.786986167797032</v>
+        <v>45.78698606445268</v>
       </c>
       <c r="N14">
-        <v>46.348084094740479</v>
+        <v>46.34808388121058</v>
       </c>
       <c r="O14">
-        <v>46.797596832497298</v>
+        <v>46.79759678874583</v>
       </c>
       <c r="P14">
-        <v>49.449083535007397</v>
+        <v>49.44908417976131</v>
       </c>
       <c r="Q14">
-        <v>51.635485332888088</v>
+        <v>51.63548603755377</v>
       </c>
       <c r="R14">
-        <v>53.104531458159137</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
+        <v>53.1045321682244</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>51.194067860218439</v>
+        <v>51.19406783748532</v>
       </c>
       <c r="C15">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D15">
-        <v>58.344848179560913</v>
+        <v>58.34484816958646</v>
       </c>
       <c r="E15">
-        <v>53.745211230547348</v>
+        <v>53.74521121773206</v>
       </c>
       <c r="F15">
-        <v>49.855413094787757</v>
-      </c>
-      <c r="G15" s="2">
-        <v>48.604980432339147</v>
+        <v>49.855413070339</v>
+      </c>
+      <c r="G15">
+        <v>48.60498040095916</v>
       </c>
       <c r="H15">
-        <v>46.911499042767268</v>
+        <v>46.91149904735532</v>
       </c>
       <c r="I15">
-        <v>45.965655327828813</v>
+        <v>45.9656553697166</v>
       </c>
       <c r="J15">
-        <v>45.705105951032543</v>
+        <v>45.70510600559214</v>
       </c>
       <c r="K15">
-        <v>44.903397136933307</v>
+        <v>44.90339719170442</v>
       </c>
       <c r="L15">
-        <v>44.854229686454957</v>
+        <v>44.85422973840584</v>
       </c>
       <c r="M15">
-        <v>45.648062160115202</v>
+        <v>45.6480620980562</v>
       </c>
       <c r="N15">
-        <v>46.207277790606703</v>
+        <v>46.20727764715218</v>
       </c>
       <c r="O15">
-        <v>46.747576123571299</v>
+        <v>46.747576128145</v>
       </c>
       <c r="P15">
-        <v>50.350205590985681</v>
+        <v>50.35020624593002</v>
       </c>
       <c r="Q15">
-        <v>52.430071461065722</v>
+        <v>52.43007213768833</v>
       </c>
       <c r="R15">
-        <v>52.422533716367823</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
+        <v>52.42253479291657</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>50.620177405974857</v>
+        <v>50.62017738885307</v>
       </c>
       <c r="C16">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D16">
-        <v>58.212572116913748</v>
+        <v>58.212572107563</v>
       </c>
       <c r="E16">
-        <v>53.583947016562938</v>
+        <v>53.58394700521846</v>
       </c>
       <c r="F16">
-        <v>49.69365361285719</v>
-      </c>
-      <c r="G16" s="2">
-        <v>48.452255785782349</v>
+        <v>49.6936535896945</v>
+      </c>
+      <c r="G16">
+        <v>48.45225575671199</v>
       </c>
       <c r="H16">
-        <v>46.671792219847802</v>
+        <v>46.67179221605014</v>
       </c>
       <c r="I16">
-        <v>45.565757694991127</v>
+        <v>45.56575772668223</v>
       </c>
       <c r="J16">
-        <v>45.284053014654127</v>
+        <v>45.28405304966741</v>
       </c>
       <c r="K16">
-        <v>44.615241104142633</v>
+        <v>44.61524118788576</v>
       </c>
       <c r="L16">
-        <v>44.50623619150246</v>
+        <v>44.50623630878684</v>
       </c>
       <c r="M16">
-        <v>45.182695751086747</v>
+        <v>45.18269567561418</v>
       </c>
       <c r="N16">
-        <v>45.747147122262369</v>
+        <v>45.74714696537261</v>
       </c>
       <c r="O16">
-        <v>46.392514240311712</v>
+        <v>46.39251418224362</v>
       </c>
       <c r="P16">
-        <v>50.39525534232753</v>
+        <v>50.39525602202452</v>
       </c>
       <c r="Q16">
-        <v>52.71475220214576</v>
+        <v>52.71475289099362</v>
       </c>
       <c r="R16">
-        <v>52.602986907368631</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
+        <v>52.60298772257163</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>50.203291883386918</v>
+        <v>50.20329186319073</v>
       </c>
       <c r="C17">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D17" s="3">
-        <v>58.210274843921219</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D17">
+        <v>58.21027483390532</v>
       </c>
       <c r="E17">
-        <v>53.607530567355049</v>
+        <v>53.60753055398444</v>
       </c>
       <c r="F17">
-        <v>49.550370080912053</v>
-      </c>
-      <c r="G17" s="2">
-        <v>48.291222335657302</v>
+        <v>49.55037006061707</v>
+      </c>
+      <c r="G17">
+        <v>48.29122230732926</v>
       </c>
       <c r="H17">
-        <v>46.625532937968217</v>
+        <v>46.62553293964875</v>
       </c>
       <c r="I17">
-        <v>45.602029296919191</v>
+        <v>45.60202932833801</v>
       </c>
       <c r="J17">
-        <v>45.381365775320504</v>
+        <v>45.38136581500058</v>
       </c>
       <c r="K17">
-        <v>44.599792903587563</v>
+        <v>44.5997929209715</v>
       </c>
       <c r="L17">
-        <v>44.554783631661998</v>
+        <v>44.55478362812253</v>
       </c>
       <c r="M17">
-        <v>45.245981161929024</v>
+        <v>45.24598108481945</v>
       </c>
       <c r="N17">
-        <v>45.825899620846862</v>
+        <v>45.82589946876082</v>
       </c>
       <c r="O17">
-        <v>46.377416607051742</v>
+        <v>46.37741659808847</v>
       </c>
       <c r="P17">
-        <v>50.030390165461498</v>
+        <v>50.03039087843008</v>
       </c>
       <c r="Q17">
-        <v>52.569181764483467</v>
+        <v>52.56918250323812</v>
       </c>
       <c r="R17">
-        <v>52.592528662943522</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
+        <v>52.59252959694918</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>53.648264147288707</v>
+        <v>53.64826408250607</v>
       </c>
       <c r="C18">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D18" s="2">
-        <v>52.253221866165347</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D18">
+        <v>52.25322183871941</v>
       </c>
       <c r="E18">
-        <v>53.42859821582578</v>
-      </c>
-      <c r="F18" s="3">
-        <v>51.999339725005314</v>
+        <v>53.428598102367</v>
+      </c>
+      <c r="F18">
+        <v>51.99933965602146</v>
       </c>
       <c r="G18">
-        <v>51.274520765459073</v>
+        <v>51.27452073957404</v>
       </c>
       <c r="H18">
-        <v>48.546093275547747</v>
+        <v>48.54609315236615</v>
       </c>
       <c r="I18">
-        <v>48.753648112608211</v>
+        <v>48.75364790138279</v>
       </c>
       <c r="J18">
-        <v>47.871828859871037</v>
+        <v>47.87182874695402</v>
       </c>
       <c r="K18">
-        <v>48.695631241713699</v>
+        <v>48.69563095893463</v>
       </c>
       <c r="L18">
-        <v>49.971469452284609</v>
+        <v>49.97147002272889</v>
       </c>
       <c r="M18">
-        <v>52.344240596338388</v>
+        <v>52.34424073199564</v>
       </c>
       <c r="N18">
-        <v>53.82767930694741</v>
+        <v>53.82767956801612</v>
       </c>
       <c r="O18">
-        <v>54.288312478467688</v>
+        <v>54.28831312725103</v>
       </c>
       <c r="P18">
-        <v>53.511784048652729</v>
+        <v>53.51178484376333</v>
       </c>
       <c r="Q18">
-        <v>53.917993861525517</v>
+        <v>53.91799480961469</v>
       </c>
       <c r="R18">
-        <v>54.715177129272128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
+        <v>54.71517787264847</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>53.510989005867799</v>
+        <v>53.510988612753</v>
       </c>
       <c r="C19">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D19">
-        <v>52.215112618196507</v>
+        <v>52.21511260214561</v>
       </c>
       <c r="E19">
-        <v>53.052092923281343</v>
-      </c>
-      <c r="F19" s="2">
-        <v>51.250706106532498</v>
-      </c>
-      <c r="G19" s="3">
-        <v>49.925656869314111</v>
+        <v>53.05209288412473</v>
+      </c>
+      <c r="F19">
+        <v>51.25070608251675</v>
+      </c>
+      <c r="G19">
+        <v>49.92565690770267</v>
       </c>
       <c r="H19">
-        <v>47.176368637555441</v>
+        <v>47.1763682943178</v>
       </c>
       <c r="I19">
-        <v>47.918328772468961</v>
+        <v>47.91832881221349</v>
       </c>
       <c r="J19">
-        <v>47.073180140277351</v>
+        <v>47.07318019476727</v>
       </c>
       <c r="K19">
-        <v>47.711549441458729</v>
+        <v>47.71154959105966</v>
       </c>
       <c r="L19">
-        <v>49.557319851689137</v>
+        <v>49.55732029352476</v>
       </c>
       <c r="M19">
-        <v>50.280457500208783</v>
+        <v>50.28045823371908</v>
       </c>
       <c r="N19">
-        <v>52.144864478639441</v>
+        <v>52.14486584586592</v>
       </c>
       <c r="O19">
-        <v>52.5809140451587</v>
+        <v>52.58091578274117</v>
       </c>
       <c r="P19">
-        <v>53.708710025543787</v>
+        <v>53.70871277613074</v>
       </c>
       <c r="Q19">
-        <v>54.413596196644619</v>
+        <v>54.4135998300902</v>
       </c>
       <c r="R19">
-        <v>56.226361730844843</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>36</v>
+        <v>56.22636655457399</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>53.141105606516653</v>
+        <v>53.14110562704395</v>
       </c>
       <c r="C20">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D20" s="3">
-        <v>52.189512619855961</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D20">
+        <v>52.18951260742502</v>
       </c>
       <c r="E20">
-        <v>52.321023168570989</v>
+        <v>52.32102314482422</v>
       </c>
       <c r="F20">
-        <v>50.858890999242128</v>
-      </c>
-      <c r="G20" s="2">
-        <v>48.215759071470238</v>
+        <v>50.85889096670021</v>
+      </c>
+      <c r="G20">
+        <v>48.2157590695579</v>
       </c>
       <c r="H20">
-        <v>47.086251511839109</v>
+        <v>47.08625151831039</v>
       </c>
       <c r="I20">
-        <v>46.384639769737262</v>
+        <v>46.38463978808128</v>
       </c>
       <c r="J20">
-        <v>47.024666909373813</v>
+        <v>47.02466724200277</v>
       </c>
       <c r="K20">
-        <v>47.381363390117457</v>
+        <v>47.38136352397303</v>
       </c>
       <c r="L20">
-        <v>48.825478705142572</v>
+        <v>48.82547915793524</v>
       </c>
       <c r="M20">
-        <v>49.742580692755887</v>
+        <v>49.74258174162555</v>
       </c>
       <c r="N20">
-        <v>50.856578214723513</v>
+        <v>50.85657959590039</v>
       </c>
       <c r="O20">
-        <v>51.466210857281581</v>
+        <v>51.46621296214356</v>
       </c>
       <c r="P20">
-        <v>52.076820127460891</v>
+        <v>52.07682270708904</v>
       </c>
       <c r="Q20">
-        <v>53.709782846081048</v>
+        <v>53.70978686588212</v>
       </c>
       <c r="R20">
-        <v>55.987894290846597</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>37</v>
+        <v>55.98789587973024</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>55.781047586584933</v>
+        <v>55.78104782134307</v>
       </c>
       <c r="C21">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D21" s="2">
-        <v>56.965799046237947</v>
-      </c>
-      <c r="E21" s="3">
-        <v>52.830966357358292</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D21">
+        <v>56.96579932802934</v>
+      </c>
+      <c r="E21">
+        <v>52.83096629654036</v>
       </c>
       <c r="F21">
-        <v>53.039702917827313</v>
+        <v>53.0397028576125</v>
       </c>
       <c r="G21">
-        <v>53.882904835737833</v>
+        <v>53.88290470464801</v>
       </c>
       <c r="H21">
-        <v>51.846552015041361</v>
+        <v>51.84655179115828</v>
       </c>
       <c r="I21">
-        <v>53.033822099953618</v>
+        <v>53.03382196099133</v>
       </c>
       <c r="J21">
-        <v>56.053918227482001</v>
+        <v>56.05391783375899</v>
       </c>
       <c r="K21">
-        <v>56.963861818649008</v>
+        <v>56.96386161354847</v>
       </c>
       <c r="L21">
-        <v>57.531230424981217</v>
+        <v>57.53123118291388</v>
       </c>
       <c r="M21">
-        <v>58.061056669032801</v>
+        <v>58.06105646753288</v>
       </c>
       <c r="N21">
-        <v>59.763334423202473</v>
+        <v>59.76333564792532</v>
       </c>
       <c r="O21">
-        <v>60.048602659613202</v>
+        <v>60.04860342367127</v>
       </c>
       <c r="P21">
-        <v>60.115105043764331</v>
+        <v>60.11510581271444</v>
       </c>
       <c r="Q21">
-        <v>60.294685764753908</v>
+        <v>60.29468664499799</v>
       </c>
       <c r="R21">
-        <v>61.0857751227893</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>38</v>
+        <v>61.08577627510606</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>55.382171710830796</v>
+        <v>55.3821719178891</v>
       </c>
       <c r="C22">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D22" s="2">
-        <v>57.352538032853268</v>
-      </c>
-      <c r="E22" s="2">
-        <v>52.923259987592019</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D22">
+        <v>57.35253831887203</v>
+      </c>
+      <c r="E22">
+        <v>52.9232599500063</v>
       </c>
       <c r="F22">
-        <v>53.222286033206949</v>
+        <v>53.22228604298186</v>
       </c>
       <c r="G22">
-        <v>54.454104558543143</v>
+        <v>54.45410485246137</v>
       </c>
       <c r="H22">
-        <v>51.867942708506213</v>
+        <v>51.86794301817473</v>
       </c>
       <c r="I22">
-        <v>52.646322252379029</v>
+        <v>52.64632239990488</v>
       </c>
       <c r="J22">
-        <v>55.382083425967821</v>
+        <v>55.38208418358455</v>
       </c>
       <c r="K22">
-        <v>56.527218857332223</v>
+        <v>56.5272203388094</v>
       </c>
       <c r="L22">
-        <v>58.524501110971798</v>
+        <v>58.5245033806464</v>
       </c>
       <c r="M22">
-        <v>58.342317279114368</v>
+        <v>58.3423215502214</v>
       </c>
       <c r="N22">
-        <v>59.533959320766321</v>
+        <v>59.53396453046917</v>
       </c>
       <c r="O22">
-        <v>59.682117051141937</v>
+        <v>59.68212308813129</v>
       </c>
       <c r="P22">
-        <v>59.382833636199663</v>
+        <v>59.3828407012662</v>
       </c>
       <c r="Q22">
-        <v>59.492952885650922</v>
+        <v>59.49296092642464</v>
       </c>
       <c r="R22">
-        <v>61.176341274517632</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>39</v>
+        <v>61.17635049104537</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>52.42453687394454</v>
+        <v>52.42453681734297</v>
       </c>
       <c r="C23">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D23" s="2">
-        <v>52.429898890228152</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D23">
+        <v>52.42989883347732</v>
       </c>
       <c r="E23">
-        <v>52.353533035748022</v>
+        <v>52.35353295988899</v>
       </c>
       <c r="F23">
-        <v>52.331958246759463</v>
+        <v>52.33195828677083</v>
       </c>
       <c r="G23">
-        <v>51.59864968662496</v>
+        <v>51.59864952537218</v>
       </c>
       <c r="H23">
-        <v>54.081778641060367</v>
+        <v>54.08177765302547</v>
       </c>
       <c r="I23">
-        <v>53.759760876339797</v>
+        <v>53.75976000693495</v>
       </c>
       <c r="J23">
-        <v>57.173702938692912</v>
+        <v>57.17370280072853</v>
       </c>
       <c r="K23">
-        <v>58.382126361749563</v>
+        <v>58.38212756747919</v>
       </c>
       <c r="L23">
-        <v>59.11747783817372</v>
+        <v>59.11748043922539</v>
       </c>
       <c r="M23">
-        <v>60.040432950870922</v>
+        <v>60.04043823002551</v>
       </c>
       <c r="N23">
-        <v>61.622288298330822</v>
+        <v>61.62229582299037</v>
       </c>
       <c r="O23">
-        <v>63.965903211477674</v>
+        <v>63.96591264031365</v>
       </c>
       <c r="P23">
-        <v>65.740945514551413</v>
+        <v>65.74095556031411</v>
       </c>
       <c r="Q23">
-        <v>65.799417144453372</v>
+        <v>65.7994287923118</v>
       </c>
       <c r="R23">
-        <v>67.5138432433492</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>40</v>
+        <v>67.51386118206726</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>51.806423107288659</v>
+        <v>51.80642308114434</v>
       </c>
       <c r="C24">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D24" s="2">
-        <v>50.620337501091342</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D24">
+        <v>50.6203374952705</v>
       </c>
       <c r="E24">
-        <v>49.669360509897473</v>
+        <v>49.66936050006888</v>
       </c>
       <c r="F24">
-        <v>50.275831046165571</v>
+        <v>50.27583099453676</v>
       </c>
       <c r="G24">
-        <v>49.283718558203027</v>
+        <v>49.28371852713001</v>
       </c>
       <c r="H24">
-        <v>48.390939632659112</v>
+        <v>48.39093969777567</v>
       </c>
       <c r="I24">
-        <v>46.864207581043559</v>
+        <v>46.86420775094052</v>
       </c>
       <c r="J24">
-        <v>47.326838146492207</v>
+        <v>47.32683833935122</v>
       </c>
       <c r="K24">
-        <v>46.484987052459253</v>
+        <v>46.48498755023335</v>
       </c>
       <c r="L24">
-        <v>47.132020788610113</v>
+        <v>47.13202164719107</v>
       </c>
       <c r="M24">
-        <v>48.214342195628547</v>
+        <v>48.21434385361167</v>
       </c>
       <c r="N24">
-        <v>50.271889818281352</v>
+        <v>50.27189088567036</v>
       </c>
       <c r="O24">
-        <v>53.839313178565291</v>
+        <v>53.83931301130274</v>
       </c>
       <c r="P24">
-        <v>55.324031981768051</v>
+        <v>55.32403020796165</v>
       </c>
       <c r="Q24">
-        <v>56.925122472116342</v>
+        <v>56.92511966072262</v>
       </c>
       <c r="R24">
-        <v>58.459950844711521</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>41</v>
+        <v>58.45994800384433</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>51.172672177559299</v>
+        <v>51.17267216542101</v>
       </c>
       <c r="C25">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D25" s="2">
-        <v>50.406642092146413</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D25">
+        <v>50.40664208655743</v>
       </c>
       <c r="E25">
-        <v>49.363889380815017</v>
+        <v>49.3638893710733</v>
       </c>
       <c r="F25">
-        <v>49.319338885338112</v>
+        <v>49.31933884089763</v>
       </c>
       <c r="G25">
-        <v>47.755415619439987</v>
+        <v>47.75541561329636</v>
       </c>
       <c r="H25">
-        <v>47.384338202564187</v>
+        <v>47.38433822368324</v>
       </c>
       <c r="I25">
-        <v>46.529664586524113</v>
+        <v>46.52966467636021</v>
       </c>
       <c r="J25">
-        <v>47.076089355795148</v>
+        <v>47.07608951918968</v>
       </c>
       <c r="K25">
-        <v>47.405009496223492</v>
+        <v>47.40500983081807</v>
       </c>
       <c r="L25">
-        <v>46.039002302110653</v>
+        <v>46.03900307437281</v>
       </c>
       <c r="M25">
-        <v>45.553496641950566</v>
+        <v>45.55349751929152</v>
       </c>
       <c r="N25">
-        <v>47.781030100274663</v>
+        <v>47.7810306114867</v>
       </c>
       <c r="O25">
-        <v>49.475127365092042</v>
+        <v>49.47512587290768</v>
       </c>
       <c r="P25">
-        <v>53.006552229793478</v>
+        <v>53.00654943585031</v>
       </c>
       <c r="Q25">
-        <v>54.318049655978918</v>
+        <v>54.31804533910738</v>
       </c>
       <c r="R25">
-        <v>55.667578700565883</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>42</v>
+        <v>55.66757339497658</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>51.240577493509377</v>
+        <v>51.24057747578998</v>
       </c>
       <c r="C26">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D26" s="2">
-        <v>49.843422022399011</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D26">
+        <v>49.84342202149398</v>
       </c>
       <c r="E26">
-        <v>49.943280336325458</v>
+        <v>49.94328033030985</v>
       </c>
       <c r="F26">
-        <v>50.432065796903657</v>
+        <v>50.43206579872307</v>
       </c>
       <c r="G26">
-        <v>47.794350385634083</v>
+        <v>47.79435043766723</v>
       </c>
       <c r="H26">
-        <v>47.565809845678828</v>
+        <v>47.56580990154307</v>
       </c>
       <c r="I26">
-        <v>46.017862366242021</v>
+        <v>46.0178625191575</v>
       </c>
       <c r="J26">
-        <v>45.563106275809567</v>
+        <v>45.56310653859612</v>
       </c>
       <c r="K26">
-        <v>45.635001524304492</v>
+        <v>45.63500195412106</v>
       </c>
       <c r="L26">
-        <v>47.021789003061293</v>
+        <v>47.02179006400328</v>
       </c>
       <c r="M26">
-        <v>47.784881361040149</v>
+        <v>47.7848811875587</v>
       </c>
       <c r="N26">
-        <v>50.52524586190566</v>
+        <v>50.52524429178098</v>
       </c>
       <c r="O26">
-        <v>52.912196086588182</v>
+        <v>52.91219246961764</v>
       </c>
       <c r="P26">
-        <v>53.4109489080899</v>
+        <v>53.41094348288469</v>
       </c>
       <c r="Q26">
-        <v>55.673939518730563</v>
+        <v>55.6739332290462</v>
       </c>
       <c r="R26">
-        <v>57.365607978663803</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>43</v>
+        <v>57.36560026776704</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>51.114156451955601</v>
+        <v>51.11415645162266</v>
       </c>
       <c r="C27">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D27" s="2">
-        <v>49.751571991492078</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D27">
+        <v>49.75157199053811</v>
       </c>
       <c r="E27">
-        <v>49.834980513857772</v>
+        <v>49.83498050501722</v>
       </c>
       <c r="F27">
-        <v>50.303642782317461</v>
-      </c>
-      <c r="G27" s="3">
-        <v>47.593054177996713</v>
+        <v>50.30364276317835</v>
+      </c>
+      <c r="G27">
+        <v>47.59305417638081</v>
       </c>
       <c r="H27">
-        <v>47.581274464204029</v>
+        <v>47.58127445200169</v>
       </c>
       <c r="I27">
-        <v>45.951726028917193</v>
+        <v>45.95172610005999</v>
       </c>
       <c r="J27">
-        <v>45.551429224026833</v>
+        <v>45.55142930654431</v>
       </c>
       <c r="K27">
-        <v>45.354845566625869</v>
+        <v>45.35484566411866</v>
       </c>
       <c r="L27">
-        <v>45.967028191518331</v>
+        <v>45.96702859356542</v>
       </c>
       <c r="M27">
-        <v>45.902332376234583</v>
+        <v>45.90233241844849</v>
       </c>
       <c r="N27">
-        <v>46.908663064928369</v>
+        <v>46.90866276197911</v>
       </c>
       <c r="O27">
-        <v>49.801354897313722</v>
+        <v>49.80135396121882</v>
       </c>
       <c r="P27">
-        <v>50.255590075897409</v>
+        <v>50.25558831342519</v>
       </c>
       <c r="Q27">
-        <v>51.730440144260449</v>
+        <v>51.73043781750688</v>
       </c>
       <c r="R27">
-        <v>52.583693247953242</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>44</v>
+        <v>52.58369082237995</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>50.702742100694728</v>
+        <v>50.70274209203077</v>
       </c>
       <c r="C28">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D28">
-        <v>50.374802471615382</v>
+        <v>50.37480246596274</v>
       </c>
       <c r="E28">
-        <v>49.22400969111402</v>
+        <v>49.22400967960183</v>
       </c>
       <c r="F28">
-        <v>49.319172923304727</v>
-      </c>
-      <c r="G28" s="2">
-        <v>47.72594461116806</v>
+        <v>49.31917286888967</v>
+      </c>
+      <c r="G28">
+        <v>47.72594458127378</v>
       </c>
       <c r="H28">
-        <v>47.117063695169747</v>
+        <v>47.11706375654919</v>
       </c>
       <c r="I28">
-        <v>46.137099661078381</v>
+        <v>46.13709966471946</v>
       </c>
       <c r="J28">
-        <v>46.555135932713803</v>
+        <v>46.55513595416449</v>
       </c>
       <c r="K28">
-        <v>46.500716388285063</v>
+        <v>46.50071683061697</v>
       </c>
       <c r="L28">
-        <v>45.128007292453333</v>
+        <v>45.12800763299575</v>
       </c>
       <c r="M28">
-        <v>44.125708894824179</v>
+        <v>44.12570898284909</v>
       </c>
       <c r="N28">
-        <v>45.322942163054428</v>
+        <v>45.32294240917737</v>
       </c>
       <c r="O28">
-        <v>45.515108991606802</v>
+        <v>45.51510877863011</v>
       </c>
       <c r="P28">
-        <v>47.209345073403533</v>
+        <v>47.2093446614705</v>
       </c>
       <c r="Q28">
-        <v>48.248579237664551</v>
+        <v>48.24857793959582</v>
       </c>
       <c r="R28">
-        <v>50.999662638091728</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>45</v>
+        <v>50.9996596217093</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>51.115999723096799</v>
+        <v>51.11599970156097</v>
       </c>
       <c r="C29">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D29">
-        <v>50.484998178906388</v>
+        <v>50.48499817315119</v>
       </c>
       <c r="E29">
-        <v>49.369159107450898</v>
+        <v>49.36915909563167</v>
       </c>
       <c r="F29">
-        <v>49.329984240306757</v>
-      </c>
-      <c r="G29" s="2">
-        <v>47.858845323296833</v>
+        <v>49.32998418414993</v>
+      </c>
+      <c r="G29">
+        <v>47.85884528042868</v>
       </c>
       <c r="H29">
-        <v>47.391674630631357</v>
+        <v>47.39167459034484</v>
       </c>
       <c r="I29">
-        <v>46.476759421487323</v>
+        <v>46.4767594213951</v>
       </c>
       <c r="J29">
-        <v>46.965269173708862</v>
+        <v>46.96526920998159</v>
       </c>
       <c r="K29">
-        <v>46.791710976088893</v>
+        <v>46.79171140160777</v>
       </c>
       <c r="L29">
-        <v>45.57363028582364</v>
+        <v>45.57363286066344</v>
       </c>
       <c r="M29">
-        <v>44.360853868667377</v>
+        <v>44.36085419787517</v>
       </c>
       <c r="N29">
-        <v>45.519650475726543</v>
+        <v>45.51965010418995</v>
       </c>
       <c r="O29">
-        <v>45.540201515304403</v>
+        <v>45.54020048350881</v>
       </c>
       <c r="P29">
-        <v>46.86559664601829</v>
+        <v>46.86559636077763</v>
       </c>
       <c r="Q29">
-        <v>47.603919700551003</v>
+        <v>47.60391886679948</v>
       </c>
       <c r="R29">
-        <v>50.182987016400013</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>46</v>
+        <v>50.18298272968618</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>51.005713829589617</v>
+        <v>51.00571380822267</v>
       </c>
       <c r="C30">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D30">
-        <v>50.450335224050598</v>
+        <v>50.45033521834935</v>
       </c>
       <c r="E30">
-        <v>49.322526013878047</v>
+        <v>49.32252600195327</v>
       </c>
       <c r="F30">
-        <v>49.19988920897957</v>
-      </c>
-      <c r="G30" s="2">
-        <v>47.697040391449363</v>
+        <v>49.19988915723607</v>
+      </c>
+      <c r="G30">
+        <v>47.69704035808103</v>
       </c>
       <c r="H30">
-        <v>47.253590351084753</v>
+        <v>47.2535903386211</v>
       </c>
       <c r="I30">
-        <v>46.334438185945316</v>
+        <v>46.33443818025382</v>
       </c>
       <c r="J30">
-        <v>46.927895869940592</v>
+        <v>46.92789587974848</v>
       </c>
       <c r="K30">
-        <v>46.786669803767893</v>
+        <v>46.78666979419985</v>
       </c>
       <c r="L30">
-        <v>45.605672220247079</v>
+        <v>45.60567247764369</v>
       </c>
       <c r="M30">
-        <v>44.179710944677851</v>
+        <v>44.17971102383451</v>
       </c>
       <c r="N30">
-        <v>45.504142987734127</v>
+        <v>45.50414335546508</v>
       </c>
       <c r="O30">
-        <v>45.427196075696664</v>
+        <v>45.427196145858</v>
       </c>
       <c r="P30">
-        <v>46.596314103929501</v>
+        <v>46.59631373882304</v>
       </c>
       <c r="Q30">
-        <v>47.229513046472952</v>
+        <v>47.22951145004365</v>
       </c>
       <c r="R30">
-        <v>49.749055373742138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>47</v>
+        <v>49.74905279037827</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>50.743933526864957</v>
+        <v>50.74393350820565</v>
       </c>
       <c r="C31">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D31">
-        <v>50.51946096082375</v>
+        <v>50.51946095518472</v>
       </c>
       <c r="E31">
-        <v>49.443463507799592</v>
+        <v>49.44346349647844</v>
       </c>
       <c r="F31">
-        <v>49.448503886393247</v>
-      </c>
-      <c r="G31" s="2">
-        <v>47.843021477178283</v>
+        <v>49.44850383708215</v>
+      </c>
+      <c r="G31">
+        <v>47.84302144487918</v>
       </c>
       <c r="H31">
-        <v>47.285594810797257</v>
+        <v>47.28559478065375</v>
       </c>
       <c r="I31">
-        <v>46.434364173540239</v>
+        <v>46.43436416132342</v>
       </c>
       <c r="J31">
-        <v>46.918574434497593</v>
+        <v>46.91857446016625</v>
       </c>
       <c r="K31">
-        <v>46.79322154964818</v>
+        <v>46.79322181266541</v>
       </c>
       <c r="L31">
-        <v>45.737656994658728</v>
+        <v>45.73765724884208</v>
       </c>
       <c r="M31">
-        <v>44.212271152724583</v>
+        <v>44.21227125071336</v>
       </c>
       <c r="N31">
-        <v>45.376603992129631</v>
+        <v>45.37660411973982</v>
       </c>
       <c r="O31">
-        <v>45.106154351892933</v>
+        <v>45.10615426839662</v>
       </c>
       <c r="P31">
-        <v>46.192595409698733</v>
+        <v>46.19259485852429</v>
       </c>
       <c r="Q31">
-        <v>46.743492119714134</v>
+        <v>46.74349175987152</v>
       </c>
       <c r="R31">
-        <v>48.929525301242023</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>48</v>
+        <v>48.92952446563968</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>50.790900405697499</v>
+        <v>50.79090038365538</v>
       </c>
       <c r="C32">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D32">
-        <v>50.523470108745357</v>
+        <v>50.52347010312508</v>
       </c>
       <c r="E32">
-        <v>49.412688122300757</v>
+        <v>49.41268811145918</v>
       </c>
       <c r="F32">
-        <v>49.525719360147782</v>
-      </c>
-      <c r="G32" s="2">
-        <v>47.679982336906853</v>
+        <v>49.52571931243728</v>
+      </c>
+      <c r="G32">
+        <v>47.67998231030568</v>
       </c>
       <c r="H32">
-        <v>47.306882653704243</v>
+        <v>47.30688265031993</v>
       </c>
       <c r="I32">
-        <v>46.535804046909007</v>
+        <v>46.53580405584505</v>
       </c>
       <c r="J32">
-        <v>46.979812601920301</v>
+        <v>46.97981266117696</v>
       </c>
       <c r="K32">
-        <v>47.016675714309891</v>
+        <v>47.01667611848058</v>
       </c>
       <c r="L32">
-        <v>45.60147331768767</v>
+        <v>45.60147370647078</v>
       </c>
       <c r="M32">
-        <v>44.389681228284672</v>
+        <v>44.38968133396336</v>
       </c>
       <c r="N32">
-        <v>46.107962881211847</v>
+        <v>46.1079629981695</v>
       </c>
       <c r="O32">
-        <v>46.176635061394677</v>
+        <v>46.17663454542353</v>
       </c>
       <c r="P32">
-        <v>48.215692727720118</v>
+        <v>48.21569137980993</v>
       </c>
       <c r="Q32">
-        <v>48.788644537944819</v>
+        <v>48.78864219629154</v>
       </c>
       <c r="R32">
-        <v>50.471866231382513</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>49</v>
+        <v>50.47186357870216</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>50.902013568964954</v>
+        <v>50.9020135466542</v>
       </c>
       <c r="C33">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D33">
-        <v>50.552897689167317</v>
+        <v>50.55289768354497</v>
       </c>
       <c r="E33">
-        <v>49.441859904091338</v>
+        <v>49.44185989360122</v>
       </c>
       <c r="F33">
-        <v>49.286387300853782</v>
-      </c>
-      <c r="G33" s="2">
-        <v>47.794442435408612</v>
+        <v>49.28638725554606</v>
+      </c>
+      <c r="G33">
+        <v>47.79444240826746</v>
       </c>
       <c r="H33">
-        <v>47.24453301967587</v>
+        <v>47.2445330037156</v>
       </c>
       <c r="I33">
-        <v>46.463552536455019</v>
+        <v>46.46355253981589</v>
       </c>
       <c r="J33">
-        <v>46.770682438681703</v>
+        <v>46.77068249453919</v>
       </c>
       <c r="K33">
-        <v>46.815109783159407</v>
+        <v>46.81511013347482</v>
       </c>
       <c r="L33">
-        <v>45.55501499320124</v>
+        <v>45.55501530571201</v>
       </c>
       <c r="M33">
-        <v>44.506032486396251</v>
+        <v>44.50603253904921</v>
       </c>
       <c r="N33">
-        <v>45.870297770740613</v>
+        <v>45.87029791695043</v>
       </c>
       <c r="O33">
-        <v>45.975082276268282</v>
+        <v>45.97508222812267</v>
       </c>
       <c r="P33">
-        <v>48.051305273055959</v>
+        <v>48.05130434693783</v>
       </c>
       <c r="Q33">
-        <v>48.350793352272447</v>
+        <v>48.35079187366872</v>
       </c>
       <c r="R33">
-        <v>50.184660355726429</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>50</v>
+        <v>50.18465770199071</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>50.920241548279073</v>
+        <v>50.92024153873963</v>
       </c>
       <c r="C34">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D34">
-        <v>50.571766207445279</v>
+        <v>50.57176620147313</v>
       </c>
       <c r="E34">
-        <v>49.428104376232127</v>
+        <v>49.42810436478899</v>
       </c>
       <c r="F34">
-        <v>49.171186616695067</v>
-      </c>
-      <c r="G34" s="2">
-        <v>47.905890612618123</v>
+        <v>49.17118656995658</v>
+      </c>
+      <c r="G34">
+        <v>47.90589057785272</v>
       </c>
       <c r="H34">
-        <v>47.402030620968013</v>
+        <v>47.40203059608252</v>
       </c>
       <c r="I34">
-        <v>46.649310089631918</v>
+        <v>46.64931011030312</v>
       </c>
       <c r="J34">
-        <v>47.145497290478417</v>
+        <v>47.14549731436054</v>
       </c>
       <c r="K34">
-        <v>47.134558171927807</v>
+        <v>47.13455849006204</v>
       </c>
       <c r="L34">
-        <v>45.679932442367267</v>
+        <v>45.67993278132496</v>
       </c>
       <c r="M34">
-        <v>44.795241696293353</v>
+        <v>44.79524188930291</v>
       </c>
       <c r="N34">
-        <v>46.010890905376563</v>
+        <v>46.01089119018465</v>
       </c>
       <c r="O34">
-        <v>46.093864389136399</v>
+        <v>46.0938640423453</v>
       </c>
       <c r="P34">
-        <v>48.041003048894368</v>
+        <v>48.04100197567539</v>
       </c>
       <c r="Q34">
-        <v>48.096414461825518</v>
+        <v>48.09641286769254</v>
       </c>
       <c r="R34">
-        <v>49.722983306068258</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>51</v>
+        <v>49.72297972197386</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>50.965755974753492</v>
+        <v>50.96575596300013</v>
       </c>
       <c r="C35">
-        <v>72.871438056409445</v>
+        <v>72.87143805640945</v>
       </c>
       <c r="D35">
-        <v>50.51031616459332</v>
+        <v>50.51031615893169</v>
       </c>
       <c r="E35">
-        <v>49.303458474943682</v>
+        <v>49.30345846321484</v>
       </c>
       <c r="F35">
-        <v>49.013522754922228</v>
-      </c>
-      <c r="G35" s="2">
-        <v>47.599805944249368</v>
+        <v>49.01352270898681</v>
+      </c>
+      <c r="G35">
+        <v>47.59980592347457</v>
       </c>
       <c r="H35">
-        <v>47.089798248019598</v>
+        <v>47.08979822559399</v>
       </c>
       <c r="I35">
-        <v>46.061357956730618</v>
+        <v>46.06135796283014</v>
       </c>
       <c r="J35">
-        <v>46.512322249549527</v>
+        <v>46.51232226394782</v>
       </c>
       <c r="K35">
-        <v>46.334844853223267</v>
+        <v>46.3348451820322</v>
       </c>
       <c r="L35">
-        <v>45.108234326732763</v>
+        <v>45.10823461064305</v>
       </c>
       <c r="M35">
-        <v>44.107429298894068</v>
+        <v>44.1074293404094</v>
       </c>
       <c r="N35">
-        <v>45.260847888128701</v>
+        <v>45.26084801733891</v>
       </c>
       <c r="O35">
-        <v>45.388798509408282</v>
+        <v>45.38879829773539</v>
       </c>
       <c r="P35">
-        <v>47.536090477194222</v>
+        <v>47.53608942553661</v>
       </c>
       <c r="Q35">
-        <v>47.914775764151422</v>
+        <v>47.91477378203525</v>
       </c>
       <c r="R35">
-        <v>49.759600299734359</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>52</v>
+        <v>49.7595965980765</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>50.886976700381418</v>
+        <v>50.88697668899923</v>
       </c>
       <c r="C36">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D36" s="3">
-        <v>50.499795089479683</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D36">
+        <v>50.49979508344849</v>
       </c>
       <c r="E36">
-        <v>49.373942636367033</v>
+        <v>49.37394262433368</v>
       </c>
       <c r="F36">
-        <v>49.297748663934513</v>
-      </c>
-      <c r="G36" s="2">
-        <v>47.629841065057917</v>
+        <v>49.29774861309997</v>
+      </c>
+      <c r="G36">
+        <v>47.62984103152687</v>
       </c>
       <c r="H36">
-        <v>47.223525328069883</v>
+        <v>47.2235252925595</v>
       </c>
       <c r="I36">
-        <v>46.386819284447633</v>
+        <v>46.38681927367378</v>
       </c>
       <c r="J36">
-        <v>46.797859593448202</v>
+        <v>46.79785960902156</v>
       </c>
       <c r="K36">
-        <v>46.708368790754342</v>
+        <v>46.70836890427803</v>
       </c>
       <c r="L36">
-        <v>45.535947505711</v>
+        <v>45.53594781719268</v>
       </c>
       <c r="M36">
-        <v>44.253713742739663</v>
+        <v>44.25371381800962</v>
       </c>
       <c r="N36">
-        <v>45.403500350433482</v>
+        <v>45.40350055554314</v>
       </c>
       <c r="O36">
-        <v>45.283286452393661</v>
+        <v>45.28328635151742</v>
       </c>
       <c r="P36">
-        <v>46.580178990511769</v>
+        <v>46.58017504610008</v>
       </c>
       <c r="Q36">
-        <v>47.292461250774792</v>
+        <v>47.29245599832311</v>
       </c>
       <c r="R36">
-        <v>49.255758688843393</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>53</v>
+        <v>49.25575531237235</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>49.381324574752767</v>
+        <v>49.3813245752585</v>
       </c>
       <c r="C37">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D37" s="2">
-        <v>49.362855313187417</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D37">
+        <v>49.36285531432731</v>
       </c>
       <c r="E37">
-        <v>48.934095307308922</v>
+        <v>48.93409531661376</v>
       </c>
       <c r="F37">
-        <v>48.969710470727151</v>
+        <v>48.96971052951701</v>
       </c>
       <c r="G37">
-        <v>48.777826248634661</v>
+        <v>48.77782661270873</v>
       </c>
       <c r="H37">
-        <v>51.620762004157108</v>
+        <v>51.62076286145982</v>
       </c>
       <c r="I37">
-        <v>52.561967452398477</v>
+        <v>52.56196916169762</v>
       </c>
       <c r="J37">
-        <v>50.42079180338709</v>
+        <v>50.42079101604979</v>
       </c>
       <c r="K37">
-        <v>50.727779730016877</v>
+        <v>50.7277763269445</v>
       </c>
       <c r="L37">
-        <v>52.064567252436227</v>
+        <v>52.0645626919663</v>
       </c>
       <c r="M37">
-        <v>53.843140443107217</v>
+        <v>53.84313546623876</v>
       </c>
       <c r="N37">
-        <v>54.028779110348623</v>
+        <v>54.02877188548935</v>
       </c>
       <c r="O37">
-        <v>54.92403522377348</v>
+        <v>54.92402775526276</v>
       </c>
       <c r="P37">
-        <v>56.981370351889353</v>
+        <v>56.98136283527371</v>
       </c>
       <c r="Q37">
-        <v>59.171175649275277</v>
+        <v>59.17116952548513</v>
       </c>
       <c r="R37">
-        <v>60.433566983017457</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>54</v>
+        <v>60.43356097920889</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>49.52088031844368</v>
+        <v>49.52088032058063</v>
       </c>
       <c r="C38">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D38" s="2">
-        <v>49.517650875665453</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D38">
+        <v>49.51765087791003</v>
       </c>
       <c r="E38">
-        <v>48.864322320305376</v>
+        <v>48.86432230566015</v>
       </c>
       <c r="F38">
-        <v>48.551902213554307</v>
+        <v>48.55190216622492</v>
       </c>
       <c r="G38">
-        <v>48.248627183070397</v>
+        <v>48.24862729506544</v>
       </c>
       <c r="H38">
-        <v>50.093237857400723</v>
+        <v>50.093238283855</v>
       </c>
       <c r="I38">
-        <v>50.646086184350423</v>
+        <v>50.64608709322732</v>
       </c>
       <c r="J38">
-        <v>48.258962051886911</v>
+        <v>48.25896232314961</v>
       </c>
       <c r="K38">
-        <v>49.989060934287437</v>
+        <v>49.98906130425414</v>
       </c>
       <c r="L38">
-        <v>51.073275796096972</v>
+        <v>51.07327584920547</v>
       </c>
       <c r="M38">
-        <v>52.577047429493533</v>
+        <v>52.5770467757315</v>
       </c>
       <c r="N38">
-        <v>52.124054734907148</v>
+        <v>52.12405376441169</v>
       </c>
       <c r="O38">
-        <v>51.473801906296003</v>
+        <v>51.47380113518079</v>
       </c>
       <c r="P38">
-        <v>51.855978474234092</v>
+        <v>51.85597680384741</v>
       </c>
       <c r="Q38">
-        <v>53.471824896463588</v>
+        <v>53.47182523907664</v>
       </c>
       <c r="R38">
-        <v>53.05679280237834</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>55</v>
+        <v>53.05679438330368</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>49.591696644527516</v>
+        <v>49.59169665052975</v>
       </c>
       <c r="C39">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D39" s="2">
-        <v>49.590681005008669</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D39">
+        <v>49.59068100675906</v>
       </c>
       <c r="E39">
-        <v>48.882273919599662</v>
+        <v>48.88227390401625</v>
       </c>
       <c r="F39">
-        <v>48.356981561659403</v>
+        <v>48.35698151460037</v>
       </c>
       <c r="G39">
-        <v>47.765204700695222</v>
+        <v>47.76520476392769</v>
       </c>
       <c r="H39">
-        <v>48.954893256312452</v>
+        <v>48.95489354079283</v>
       </c>
       <c r="I39">
-        <v>49.181388257283743</v>
+        <v>49.18138883362052</v>
       </c>
       <c r="J39">
-        <v>47.056230864770598</v>
+        <v>47.05623110422334</v>
       </c>
       <c r="K39">
-        <v>48.24447759513717</v>
+        <v>48.24447797794853</v>
       </c>
       <c r="L39">
-        <v>50.879294786831231</v>
+        <v>50.87929534311331</v>
       </c>
       <c r="M39">
-        <v>50.630166188199688</v>
+        <v>50.63016623045269</v>
       </c>
       <c r="N39">
-        <v>51.599477452634723</v>
+        <v>51.59947732822723</v>
       </c>
       <c r="O39">
-        <v>51.380773193422627</v>
+        <v>51.38077099706309</v>
       </c>
       <c r="P39">
-        <v>53.390746521672497</v>
+        <v>53.390741204779</v>
       </c>
       <c r="Q39">
-        <v>54.362276491876081</v>
+        <v>54.36227002613921</v>
       </c>
       <c r="R39">
-        <v>56.543418181138883</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>56</v>
+        <v>56.54341415101079</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>50.864997072742732</v>
+        <v>50.8649971122034</v>
       </c>
       <c r="C40">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D40" s="2">
-        <v>50.864997072742732</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D40">
+        <v>50.8649971122034</v>
       </c>
       <c r="E40">
-        <v>50.807350878728407</v>
+        <v>50.80735085897751</v>
       </c>
       <c r="F40">
-        <v>50.76336270596849</v>
+        <v>50.76336265956616</v>
       </c>
       <c r="G40">
-        <v>50.574539908767314</v>
+        <v>50.57453995451324</v>
       </c>
       <c r="H40">
-        <v>50.600688530969627</v>
+        <v>50.60068925330732</v>
       </c>
       <c r="I40">
-        <v>52.291872886479368</v>
+        <v>52.29187435872241</v>
       </c>
       <c r="J40">
-        <v>56.603704959526759</v>
+        <v>56.60370721905891</v>
       </c>
       <c r="K40">
-        <v>58.177160110162291</v>
+        <v>58.1771648398671</v>
       </c>
       <c r="L40">
-        <v>60.080446444865672</v>
+        <v>60.08044863581078</v>
       </c>
       <c r="M40">
-        <v>61.719579034444372</v>
+        <v>61.71958024987687</v>
       </c>
       <c r="N40">
-        <v>64.638921416653403</v>
+        <v>64.63892573527556</v>
       </c>
       <c r="O40">
-        <v>68.440330224408868</v>
+        <v>68.44034011890309</v>
       </c>
       <c r="P40">
-        <v>73.110210530636479</v>
+        <v>73.11023134398877</v>
       </c>
       <c r="Q40">
-        <v>76.350009442052112</v>
+        <v>76.35002955459437</v>
       </c>
       <c r="R40">
-        <v>77.278239073745453</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>57</v>
+        <v>77.27825489248208</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>52.055362852837114</v>
+        <v>52.05536278293415</v>
       </c>
       <c r="C41">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D41" s="2">
-        <v>52.055362852837114</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D41">
+        <v>52.05536278293415</v>
       </c>
       <c r="E41">
-        <v>50.311798487745243</v>
+        <v>50.31179829199709</v>
       </c>
       <c r="F41">
-        <v>52.309887810330324</v>
+        <v>52.30988752948127</v>
       </c>
       <c r="G41">
-        <v>55.546827022190627</v>
+        <v>55.54682635718891</v>
       </c>
       <c r="H41">
-        <v>58.33929009836956</v>
+        <v>58.33928898841964</v>
       </c>
       <c r="I41">
-        <v>58.615666603093537</v>
+        <v>58.61566586504796</v>
       </c>
       <c r="J41">
-        <v>59.540500873477647</v>
+        <v>59.54050071776398</v>
       </c>
       <c r="K41">
-        <v>59.514621961131773</v>
+        <v>59.51462256712688</v>
       </c>
       <c r="L41">
-        <v>59.743020841007393</v>
+        <v>59.74302085157951</v>
       </c>
       <c r="M41">
-        <v>60.293573774988047</v>
+        <v>60.29357271449104</v>
       </c>
       <c r="N41">
-        <v>61.319262945121821</v>
+        <v>61.31926037672578</v>
       </c>
       <c r="O41">
-        <v>64.074793004005912</v>
+        <v>64.07478946035091</v>
       </c>
       <c r="P41">
-        <v>65.445259347352192</v>
+        <v>65.44525505486926</v>
       </c>
       <c r="Q41">
-        <v>66.313692788454929</v>
+        <v>66.31368727879908</v>
       </c>
       <c r="R41">
-        <v>66.4122783759925</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>58</v>
+        <v>66.41227236505571</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>56.266049154471553</v>
+        <v>56.26604935560029</v>
       </c>
       <c r="C42">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D42" s="2">
-        <v>56.562142209245643</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D42">
+        <v>56.56214255502973</v>
       </c>
       <c r="E42">
-        <v>51.409171184477998</v>
+        <v>51.40917113749111</v>
       </c>
       <c r="F42">
-        <v>52.782521767802429</v>
+        <v>52.78252162544234</v>
       </c>
       <c r="G42">
-        <v>55.193998237711511</v>
+        <v>55.19399784168044</v>
       </c>
       <c r="H42">
-        <v>53.489024099908782</v>
+        <v>53.48902339538679</v>
       </c>
       <c r="I42">
-        <v>54.26027767839328</v>
+        <v>54.26027725259071</v>
       </c>
       <c r="J42">
-        <v>54.264675957441341</v>
+        <v>54.26467551135983</v>
       </c>
       <c r="K42">
-        <v>54.971920961969232</v>
+        <v>54.97192027501936</v>
       </c>
       <c r="L42">
-        <v>59.294696773345329</v>
+        <v>59.29469550734728</v>
       </c>
       <c r="M42">
-        <v>62.560969186826497</v>
+        <v>62.56096767649472</v>
       </c>
       <c r="N42">
-        <v>64.631776594708398</v>
+        <v>64.63177320036033</v>
       </c>
       <c r="O42">
-        <v>64.316506486636527</v>
+        <v>64.31650147308599</v>
       </c>
       <c r="P42">
-        <v>64.779485195626066</v>
+        <v>64.7794804498668</v>
       </c>
       <c r="Q42">
-        <v>64.425951609371822</v>
+        <v>64.42594606008217</v>
       </c>
       <c r="R42">
-        <v>63.520928213418841</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>59</v>
+        <v>63.52092020369624</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>52.862431708290792</v>
+        <v>52.86243174991082</v>
       </c>
       <c r="C43">
-        <v>72.871438056409445</v>
-      </c>
-      <c r="D43" s="2">
-        <v>50.681055832193337</v>
+        <v>72.87143805640945</v>
+      </c>
+      <c r="D43">
+        <v>50.68105583034445</v>
       </c>
       <c r="E43">
-        <v>51.421769456810431</v>
+        <v>51.42176947051124</v>
       </c>
       <c r="F43">
-        <v>51.196027819431322</v>
+        <v>51.19602776372442</v>
       </c>
       <c r="G43">
-        <v>53.259259198385713</v>
+        <v>53.2592591935185</v>
       </c>
       <c r="H43">
-        <v>54.347502500919113</v>
+        <v>54.34750240222895</v>
       </c>
       <c r="I43">
-        <v>55.068674141240628</v>
+        <v>55.06867401716713</v>
       </c>
       <c r="J43">
-        <v>54.133916625709482</v>
+        <v>54.13391643418991</v>
       </c>
       <c r="K43">
-        <v>53.950729887173061</v>
+        <v>53.95072950393131</v>
       </c>
       <c r="L43">
-        <v>54.295734428320877</v>
+        <v>54.29573378727872</v>
       </c>
       <c r="M43">
-        <v>57.082920075708913</v>
+        <v>57.08291928101529</v>
       </c>
       <c r="N43">
-        <v>58.643379027913667</v>
+        <v>58.64337818809846</v>
       </c>
       <c r="O43">
-        <v>59.877801698948367</v>
+        <v>59.87780061841296</v>
       </c>
       <c r="P43">
-        <v>60.290158177546132</v>
+        <v>60.29015632239344</v>
       </c>
       <c r="Q43">
-        <v>60.449033980537507</v>
+        <v>60.4490308861382</v>
       </c>
       <c r="R43">
-        <v>61.339263586463389</v>
+        <v>61.33925824481777</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:R43">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>